--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T16:11:49+00:00</t>
+    <t>2025-08-01T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T13:09:58+00:00</t>
+    <t>2025-08-04T10:11:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T10:11:31+00:00</t>
+    <t>2025-08-04T13:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T13:10:17+00:00</t>
+    <t>2026-06-10T15:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Base</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Base|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:39:40+00:00</t>
+    <t>2026-06-10T15:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:45:32+00:00</t>
+    <t>2026-06-10T15:59:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:59:45+00:00</t>
+    <t>2026-06-10T16:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:12:06+00:00</t>
+    <t>2026-06-10T16:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:18:52+00:00</t>
+    <t>2026-06-11T15:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:47:13+00:00</t>
+    <t>2026-06-11T15:59:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:59:09+00:00</t>
+    <t>2026-06-11T16:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:49:00+00:00</t>
+    <t>2026-06-12T14:52:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:52:39+00:00</t>
+    <t>2026-06-12T14:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:55:33+00:00</t>
+    <t>2026-06-12T14:56:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:56:09+00:00</t>
+    <t>2026-06-12T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:58:42+00:00</t>
+    <t>2026-06-12T15:04:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:04:49+00:00</t>
+    <t>2026-06-12T15:09:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:09:19+00:00</t>
+    <t>2026-06-12T15:31:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:31:20+00:00</t>
+    <t>2026-06-12T15:45:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:45:22+00:00</t>
+    <t>2026-06-12T16:24:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T16:24:39+00:00</t>
+    <t>2026-06-16T12:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:17:15+00:00</t>
+    <t>2026-06-16T12:25:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:25:33+00:00</t>
+    <t>2026-06-17T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:47:53+00:00</t>
+    <t>2026-06-17T07:58:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:58:49+00:00</t>
+    <t>2026-06-17T08:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:05:28+00:00</t>
+    <t>2026-06-17T08:38:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:38:09+00:00</t>
+    <t>2026-06-17T08:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:46:38+00:00</t>
+    <t>2026-06-17T08:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:50:19+00:00</t>
+    <t>2026-06-17T11:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:32:53+00:00</t>
+    <t>2026-06-17T11:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:35:28+00:00</t>
+    <t>2026-06-17T11:36:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-PSIdNat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:36:10+00:00</t>
+    <t>2026-06-17T12:12:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
